--- a/AAII_Financials/Quarterly/ARGX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARGX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="92">
   <si>
     <t>ARGX</t>
   </si>
@@ -656,252 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1310600</v>
       </c>
-      <c r="E8" s="3">
-        <v>967200</v>
-      </c>
       <c r="F8" s="3">
+        <v>967600</v>
+      </c>
+      <c r="G8" s="3">
         <v>757400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>489400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>417800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>281000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>177900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>85200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>339800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>281000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>229900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>312100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>138000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>98600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>23400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>470400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>158200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>631000</v>
+      </c>
+      <c r="E9" s="3">
         <v>521400</v>
       </c>
-      <c r="E9" s="3">
-        <v>438400</v>
-      </c>
       <c r="F9" s="3">
+        <v>444100</v>
+      </c>
+      <c r="G9" s="3">
         <v>369900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>277700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>345900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>219500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>160600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>131900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>227800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>219500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>184200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1400</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
@@ -926,59 +933,62 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>910000</v>
+      </c>
+      <c r="E10" s="3">
         <v>789200</v>
       </c>
-      <c r="E10" s="3">
-        <v>528700</v>
-      </c>
       <c r="F10" s="3">
+        <v>523500</v>
+      </c>
+      <c r="G10" s="3">
         <v>387500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>211800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>72000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-46700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>112100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>61500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>45700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>289100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>127700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>92200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1003,8 +1013,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,85 +1045,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E12" s="3">
         <v>371700</v>
       </c>
-      <c r="E12" s="3">
-        <v>327700</v>
-      </c>
       <c r="F12" s="3">
+        <v>332900</v>
+      </c>
+      <c r="G12" s="3">
         <v>297200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>225300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>306400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>195500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>147800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>126900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>191800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>195500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>165900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>284200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>236700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>277000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>152000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>304700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>139400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>272100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>122300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>180000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>87200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>188000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>104700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>118700</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,35 +1203,38 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-11600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-3800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>-14400</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-5500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1224,8 +1244,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1236,14 +1256,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1263,85 +1283,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
-        <v>6600</v>
-      </c>
       <c r="F15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>101300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>3100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>1800</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>1600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>1200</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,162 +1392,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E17" s="3">
         <v>951000</v>
       </c>
-      <c r="E17" s="3">
-        <v>763300</v>
-      </c>
       <c r="F17" s="3">
+        <v>768900</v>
+      </c>
+      <c r="G17" s="3">
         <v>655800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>533400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>554700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>381500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>295900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>259700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>419700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>381500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>333400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>635200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>346600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>495900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>246100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>470700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>213800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>375300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>158200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>272200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>246600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E18" s="3">
         <v>359600</v>
       </c>
-      <c r="E18" s="3">
-        <v>203800</v>
-      </c>
       <c r="F18" s="3">
+        <v>198800</v>
+      </c>
+      <c r="G18" s="3">
         <v>101600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-43900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-136800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-118000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-174500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-79800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-103500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-323100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-397300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-222700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-443800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-212900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>95100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-255600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-118700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-221900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-106500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,191 +1582,198 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>12800</v>
       </c>
-      <c r="E20" s="3">
-        <v>-45800</v>
-      </c>
       <c r="F20" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="G20" s="3">
         <v>57700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-58700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>46200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>33300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-49800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-31900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-29300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-125600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>492500</v>
+      </c>
+      <c r="E21" s="3">
         <v>348600</v>
       </c>
-      <c r="E21" s="3">
-        <v>256300</v>
-      </c>
       <c r="F21" s="3">
+        <v>255100</v>
+      </c>
+      <c r="G21" s="3">
         <v>44300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-49100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-75500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-102700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-219200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-87900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-102700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-67400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-177900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>-444000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>-469900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>79000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>-377300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-222400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-111300</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>-100</v>
       </c>
-      <c r="E22" s="3">
-        <v>1100</v>
-      </c>
       <c r="F22" s="3">
+        <v>900</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>-1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
@@ -1742,7 +1782,7 @@
         <v>200</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1780,162 +1820,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E23" s="3">
         <v>403300</v>
       </c>
-      <c r="E23" s="3">
-        <v>286900</v>
-      </c>
       <c r="F23" s="3">
+        <v>286600</v>
+      </c>
+      <c r="G23" s="3">
         <v>86500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-61200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-83900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-217000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-83300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-83900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-76200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-282300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-241000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-447100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-230100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-475700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-230900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>76000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-29200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-381300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-183800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-224100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-87100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-113400</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-129700</v>
       </c>
-      <c r="E24" s="3">
-        <v>41500</v>
-      </c>
       <c r="F24" s="3">
+        <v>41100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-687700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-44100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-8200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-47300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-8600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,162 +2060,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E26" s="3">
         <v>533000</v>
       </c>
-      <c r="E26" s="3">
-        <v>245400</v>
-      </c>
       <c r="F26" s="3">
+        <v>245500</v>
+      </c>
+      <c r="G26" s="3">
         <v>774200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-99200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-94400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-208800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-72600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-94400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-273700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-435900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-227200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-471400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-233600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>63200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-40400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-381900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-184300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-226600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E27" s="3">
         <v>533000</v>
       </c>
-      <c r="E27" s="3">
-        <v>245400</v>
-      </c>
       <c r="F27" s="3">
+        <v>245500</v>
+      </c>
+      <c r="G27" s="3">
         <v>774200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-99200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-94400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-208800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-72600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-94400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-273700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-435900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-227200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-471400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-233600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>63200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-40400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-381900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-184300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-226600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2300,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2319,8 +2380,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2460,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,162 +2540,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12800</v>
       </c>
-      <c r="E32" s="3">
-        <v>45800</v>
-      </c>
       <c r="F32" s="3">
+        <v>49900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-57700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>58700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-46200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-33300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>49800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>31900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>29300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>125600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>65000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E33" s="3">
         <v>533000</v>
       </c>
-      <c r="E33" s="3">
-        <v>245400</v>
-      </c>
       <c r="F33" s="3">
+        <v>245500</v>
+      </c>
+      <c r="G33" s="3">
         <v>774200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-99200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-94400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-208800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-72600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-94400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-273700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-435900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-227200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-471400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-233600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>63200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-40400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-381900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-184300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-226600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,167 +2780,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E35" s="3">
         <v>533000</v>
       </c>
-      <c r="E35" s="3">
-        <v>245400</v>
-      </c>
       <c r="F35" s="3">
+        <v>245500</v>
+      </c>
+      <c r="G35" s="3">
         <v>774200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-99200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-94400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-208800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-72600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-94400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-273700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-435900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-227200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-471400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-233600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>63200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-40400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-381900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-184300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-226600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +2977,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,44 +3007,45 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3584000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3491300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2086000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1499900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1438200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2048800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1110600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1367300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>1110600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2998,46 +3085,49 @@
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="E42" s="3">
         <v>948800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1842200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1878900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1664100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1131000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>886400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1391800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1230100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>886400</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>5</v>
@@ -3075,44 +3165,47 @@
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1941000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1657100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1198200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>909100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>655600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>499300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>354600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>277300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>354600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -3152,44 +3245,47 @@
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E44" s="3">
         <v>473500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>340600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>407200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>326500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>310600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>201100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>228400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>135700</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>201100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3229,8 +3325,11 @@
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3306,44 +3405,47 @@
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8068000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6899100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5829700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4883100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4263800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4123700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2691500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2774200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2929300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3">
         <v>2691500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3383,44 +3485,47 @@
       <c r="AA46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>50500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>38600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>49900</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3460,44 +3565,47 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E48" s="3">
         <v>48200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>14700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3537,46 +3645,49 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E49" s="3">
         <v>272100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>219000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>181400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>141800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>125200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>189900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>174900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>171300</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>189900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
@@ -3614,8 +3725,11 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3805,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,44 +3885,47 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E52" s="3">
         <v>116900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>170800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>120500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>140800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>126500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>109100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>49200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>109100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3845,8 +3965,11 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,44 +4045,47 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10032000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8682700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7175600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6202500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4796600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4542500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3193800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3134300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3249300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>3193800</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3999,8 +4125,11 @@
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4157,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,44 +4187,45 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>719000</v>
+      </c>
+      <c r="E57" s="3">
         <v>554300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>532000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>342200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>280600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>245600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>195300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>188700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>195300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4134,46 +4265,49 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>3200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>5</v>
@@ -4211,44 +4345,47 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E59" s="3">
         <v>140700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>54400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>10000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4288,44 +4425,47 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1575000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1320200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1041900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>669900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>499600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>423000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>317800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>302300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>264600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3">
         <v>317800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4365,44 +4505,47 @@
       <c r="AA60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>8000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4442,8 +4585,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4519,8 +4665,11 @@
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4745,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4825,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,44 +4905,47 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1615000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1359600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1079800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>704200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>534300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>445000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>335700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>320600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>279000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>335700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4827,8 +4985,11 @@
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5017,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5095,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5175,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5087,8 +5255,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,44 +5335,47 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>558000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-279800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1157000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1571800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2437400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2404800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2233000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2109800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1836100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>-2233000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -5241,8 +5415,11 @@
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5495,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5575,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,47 +5655,50 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8417000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7323100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6095800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5498300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4262200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4097500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2858100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2813700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2970300</v>
-      </c>
-      <c r="L76" s="3">
-        <v>2858100</v>
       </c>
       <c r="M76" s="3">
         <v>2858100</v>
       </c>
       <c r="N76" s="3">
+        <v>2858100</v>
+      </c>
+      <c r="O76" s="3">
         <v>2813700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5549,8 +5735,11 @@
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,167 +5815,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E81" s="3">
         <v>533000</v>
       </c>
-      <c r="E81" s="3">
-        <v>245400</v>
-      </c>
       <c r="F81" s="3">
+        <v>245500</v>
+      </c>
+      <c r="G81" s="3">
         <v>774200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-99200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-94400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-208800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-72600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-94400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-273700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-435900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-227200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-471400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-233600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>63200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-40400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-381900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-184300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-226600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-117800</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,8 +6012,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5852,47 +6051,50 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>104300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>3100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>5900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>3000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>3900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6170,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6250,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6330,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6410,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,8 +6490,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6314,47 +6531,50 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>-862800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>-494500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>-606800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>-225100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>-346300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-136000</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,8 +6602,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6420,8 +6641,8 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6439,28 +6660,31 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6760,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,8 +6840,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6651,47 +6881,50 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-461200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-232300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-347100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-492300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>344700</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>303000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,8 +6952,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6757,8 +6991,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6796,8 +7030,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7110,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7190,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,8 +7270,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7065,47 +7311,50 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>843800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>808300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>1121300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>1103300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>833000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>816600</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7142,47 +7391,50 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-53700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-48800</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-49600</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-20800</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>65400</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>3500</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7219,43 +7471,46 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>-533900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>32600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>117900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>365100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>844600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>973200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
